--- a/data/official_data/knowledge/programme_mapping.xlsx
+++ b/data/official_data/knowledge/programme_mapping.xlsx
@@ -2182,7 +2182,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="270" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="186" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>6</v>
       </c>
